--- a/output/topology_excel/943.xlsx
+++ b/output/topology_excel/943.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -517,21 +517,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -553,7 +553,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,18 +586,18 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -608,18 +608,18 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -630,18 +630,18 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -652,32 +652,32 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Door</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>403</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,10 +696,10 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>196</v>
+        <v>247</v>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>155</v>
+        <v>254</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -729,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>183</v>
+        <v>48</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>118</v>
+        <v>264</v>
       </c>
       <c r="F15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -773,7 +773,7 @@
         <v>2</v>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>169</v>
+        <v>403</v>
       </c>
       <c r="F16" t="n">
         <v>12</v>
@@ -795,7 +795,7 @@
         <v>2</v>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,18 +806,18 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>438</v>
+        <v>58</v>
       </c>
       <c r="F17" t="n">
-        <v>307</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,18 +828,18 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>189</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>160</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,10 +872,10 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>30</v>
+        <v>146</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -883,7 +883,7 @@
         <v>3</v>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,10 +894,10 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>350</v>
+        <v>30</v>
       </c>
       <c r="F21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -905,7 +905,7 @@
         <v>4</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="F22" t="n">
         <v>30</v>
@@ -927,7 +927,7 @@
         <v>4</v>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="F23" t="n">
         <v>30</v>
@@ -946,10 +946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,18 +960,18 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="F25" t="n">
         <v>11</v>
@@ -990,10 +990,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="F26" t="n">
         <v>11</v>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,18 +1026,18 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="F27" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,19 +1048,19 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="F28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" t="n">
         <v>8</v>
       </c>
-      <c r="B29" t="n">
-        <v>10</v>
-      </c>
       <c r="C29" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="F29" t="n">
         <v>12</v>
@@ -1078,11 +1078,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" t="n">
         <v>9</v>
       </c>
-      <c r="B30" t="n">
-        <v>11</v>
-      </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1092,10 +1092,318 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
+        <v>146</v>
+      </c>
+      <c r="F30" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>169</v>
+      </c>
+      <c r="F31" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>169</v>
+      </c>
+      <c r="F32" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" t="n">
+        <v>14</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>297</v>
+      </c>
+      <c r="F33" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" t="n">
+        <v>15</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>196</v>
+      </c>
+      <c r="F34" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" t="n">
+        <v>12</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>147</v>
+      </c>
+      <c r="F35" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>8</v>
+      </c>
+      <c r="B36" t="n">
+        <v>9</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>178</v>
+      </c>
+      <c r="F36" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" t="n">
+        <v>13</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>350</v>
+      </c>
+      <c r="F37" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>11</v>
+      </c>
+      <c r="B38" t="n">
+        <v>13</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>169</v>
+      </c>
+      <c r="F38" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" t="n">
+        <v>15</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
         <v>135</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F39" t="n">
         <v>15</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" t="n">
+        <v>14</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>253</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>120</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" t="n">
+        <v>8</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>69</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>248</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" t="n">
+        <v>8</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>32</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/943.xlsx
+++ b/output/topology_excel/943.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
         <v>196</v>
       </c>
       <c r="F34" t="n">
-        <v>150</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35">
